--- a/重大节点进度追踪通报及存档汇总/各专业反馈标注的汇总表/污水站土建完成节点汇总_20260813（污水回复）.xlsx
+++ b/重大节点进度追踪通报及存档汇总/各专业反馈标注的汇总表/污水站土建完成节点汇总_20260813（污水回复）.xlsx
@@ -4498,7 +4498,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F134" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:F44 A45:B45 D45:F45 A46:F134" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>